--- a/DataTables/DetailText/剧情/016雷万钧归来.xlsx
+++ b/DataTables/DetailText/剧情/016雷万钧归来.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FDAB4E-CB52-4D5D-A8BC-C1AA2B19BE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D4045C-CF7B-460B-A34D-FE24965CFA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2370" yWindow="1995" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="58">
   <si>
     <t>StoryID</t>
   </si>
@@ -238,6 +227,277 @@
   </si>
   <si>
     <t>看来这事远比我们想的复杂…</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>放任不管的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，是要出大事的...</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>我想到了一个能帮上忙的人。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>哦？是谁？</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楚王。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>弟</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>认识这么大的人物</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>之前医治过世子，应该能说得上话。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>那还等什么，我陪你现在就去！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>一路无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>话</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，两人来到了楚王府</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楚王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>前日一别，先生别来无恙啊。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>先生是犬子的救命恩人，有什么本王能帮上忙的一定尽力而为。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>李</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>东</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>璧将事情的前因后果如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>了楚王</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>草民拜见王</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，今日来是有一事</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>王</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans JP"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>帮忙。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/016/016_01.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/016/016_02.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -245,11 +505,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +523,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -284,7 +544,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -309,6 +569,13 @@
       <color theme="1"/>
       <name val="Noto Sans JP"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -371,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -427,9 +694,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -708,27 +978,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -778,7 +1048,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16">
       <c r="A2" s="16" t="s">
         <v>31</v>
       </c>
@@ -814,65 +1084,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="9"/>
       <c r="H3" s="13"/>
       <c r="L3" s="17"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16">
       <c r="C4" s="9"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16">
       <c r="C5" s="9"/>
       <c r="H5" s="13"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16">
       <c r="C6" s="9"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16">
       <c r="C7" s="9"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16">
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16">
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16">
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16">
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16">
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16">
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16">
       <c r="H14" s="13"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16">
       <c r="H15" s="13"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16">
       <c r="H16" s="13"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="13"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="13"/>
     </row>
   </sheetData>
@@ -883,21 +1153,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -923,7 +1193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -941,7 +1211,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -961,7 +1231,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -981,7 +1251,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1001,7 +1271,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1021,7 +1291,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1041,7 +1311,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1057,46 +1327,313 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H8" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H9" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>